--- a/results/tables/04_community_composition_measures/table1_species_pc_loadings.xlsx
+++ b/results/tables/04_community_composition_measures/table1_species_pc_loadings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,11 +469,6 @@
           <t>PC6</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>PC7</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -485,25 +480,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.7458</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5214</v>
+        <v>-0.1979</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1035</v>
+        <v>-0.2199</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0131</v>
+        <v>0.4289</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2544</v>
+        <v>-0.1696</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3619</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-0.1815</v>
+        <v>-0.2258</v>
       </c>
     </row>
     <row r="3">
@@ -512,29 +504,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1021</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4493</v>
+        <v>-0.5841</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2344</v>
+        <v>-0.1397</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1719</v>
+        <v>0.505</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1692</v>
+        <v>-0.1405</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2957</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.4786</v>
+        <v>-0.0472</v>
       </c>
     </row>
     <row r="4">
@@ -543,29 +532,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.1683</v>
+        <v>0.2174</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0344</v>
+        <v>-0.2831</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1718</v>
+        <v>-0.1315</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4159</v>
+        <v>-0.0973</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5493</v>
+        <v>-0.0673</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3267</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-0.1987</v>
+        <v>0.8593</v>
       </c>
     </row>
     <row r="5">
@@ -574,29 +560,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2443</v>
+        <v>0.1421</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2252</v>
+        <v>-0.2003</v>
       </c>
       <c r="E5" t="n">
-        <v>0.68</v>
+        <v>0.9321</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0233</v>
+        <v>0.1673</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0555</v>
+        <v>0.0927</v>
       </c>
       <c r="H5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.1377</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="6">
@@ -605,29 +588,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.3449</v>
+        <v>-0.2225</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5399</v>
+        <v>0.5858</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2238</v>
+        <v>0.029</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2883</v>
+        <v>0.452</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0076</v>
+        <v>-0.0264</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0975</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.2117</v>
+        <v>0.2382</v>
       </c>
     </row>
     <row r="7">
@@ -636,29 +616,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0226</v>
+        <v>-0.1064</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0604</v>
+        <v>-0.3015</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2869</v>
+        <v>-0.0837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7050999999999999</v>
+        <v>-0.351</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2459</v>
+        <v>0.3591</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.354</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0002</v>
+        <v>-0.06469999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -667,29 +644,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.3533</v>
+        <v>0.03</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1152</v>
+        <v>0.117</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1715</v>
+        <v>-0.0752</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0027</v>
+        <v>0.3478</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1557</v>
+        <v>0.4481</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0829</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.2153</v>
       </c>
     </row>
     <row r="9">
@@ -698,29 +672,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1666</v>
+        <v>0.094</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.208</v>
+        <v>-0.0299</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1909</v>
+        <v>-0.1201</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1217</v>
+        <v>0.7318</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.183</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.4273</v>
+        <v>-0.1231</v>
       </c>
     </row>
     <row r="10">
@@ -729,29 +700,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.2933</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.214</v>
+        <v>-0.1703</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3218</v>
+        <v>0.0104</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2355</v>
+        <v>0.195</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0176</v>
+        <v>0.0809</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0447</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.1525</v>
+        <v>-0.0417</v>
       </c>
     </row>
     <row r="11">
@@ -760,29 +728,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0374</v>
+        <v>-0.0197</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1069</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1183</v>
+        <v>0.0465</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1717</v>
+        <v>-0.0396</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5851</v>
+        <v>0.0747</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1372</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.118</v>
+        <v>0.2485</v>
       </c>
     </row>
     <row r="12">
@@ -791,29 +756,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.2271</v>
+        <v>0.0416</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.197</v>
+        <v>0.0369</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1273</v>
+        <v>-0.0138</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0756</v>
+        <v>0.1054</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2119</v>
+        <v>0.179</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2629</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.1325</v>
+        <v>0.0473</v>
       </c>
     </row>
     <row r="13">
@@ -822,29 +784,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.3341</v>
+        <v>-0.0397</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0235</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.161</v>
+        <v>0.103</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2843</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2177</v>
+        <v>0.0444</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.1551</v>
+        <v>-0.07489999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -853,29 +812,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.25</v>
+        <v>-0.0281</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0298</v>
+        <v>-0.0047</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2017</v>
+        <v>-0.0605</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0322</v>
+        <v>0.0725</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1725</v>
+        <v>0.0975</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4043</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0641</v>
+        <v>0.1087</v>
       </c>
     </row>
     <row r="15">
@@ -888,25 +844,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.055</v>
+        <v>0.0191</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0446</v>
+        <v>-0.0438</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1892</v>
+        <v>0.018</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1354</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0418</v>
+        <v>0.0912</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.168</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.1599</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="16">
@@ -915,29 +868,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0352</v>
+        <v>-0.0362</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1392</v>
+        <v>-0.0735</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0614</v>
+        <v>-0.0293</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1108</v>
+        <v>-0.0257</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1744</v>
+        <v>0.0258</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0289</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0905</v>
+        <v>-0.0014</v>
       </c>
     </row>
     <row r="17">
@@ -946,29 +896,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.0285</v>
+        <v>0.0658</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0617</v>
+        <v>0.0028</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0653</v>
+        <v>-0.0134</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0785</v>
+        <v>0.0005</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0732</v>
+        <v>0.0877</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0738</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.014</v>
+        <v>-0.0039</v>
       </c>
     </row>
     <row r="18">
@@ -977,26 +924,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0318</v>
+        <v>-0.1664</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3615</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3629</v>
+        <v>0.2279</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5935</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.5124</v>
-      </c>
+        <v>-0.4487</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1008,22 +952,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.649</v>
+        <v>-0.2357</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1125</v>
+        <v>0.5465</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4104</v>
+        <v>0.1095</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0478</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.3939</v>
-      </c>
+        <v>0.6361</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1031,26 +972,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6692</v>
+        <v>0.7254</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3492</v>
+        <v>0.1614</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4567</v>
+        <v>-0.207</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.029</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.1023</v>
-      </c>
+        <v>0.1391</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1058,26 +996,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.1957</v>
+        <v>0.3437</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5876</v>
+        <v>0.049</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2206</v>
+        <v>0.4576</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1236</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-0.4346</v>
-      </c>
+        <v>0.2351</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1085,26 +1020,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0295</v>
+        <v>0.16</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1113</v>
+        <v>-0.1452</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3554</v>
+        <v>0.4732</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6241</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.2688</v>
-      </c>
+        <v>-0.1465</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1112,26 +1044,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0764</v>
+        <v>-0.4716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3668</v>
+        <v>-0.293</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4262</v>
+        <v>0.0757</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3087</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.002</v>
-      </c>
+        <v>0.0606</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1139,26 +1068,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.0689</v>
+        <v>-0.0468</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1579</v>
+        <v>-0.179</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1118</v>
+        <v>0.5078</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1986</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.367</v>
-      </c>
+        <v>0.1318</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1166,26 +1092,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.1821</v>
+        <v>0.1152</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0161</v>
+        <v>0.0267</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2462</v>
+        <v>0.1274</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1038</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.245</v>
-      </c>
+        <v>-0.4655</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1193,26 +1116,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1023</v>
+        <v>0.0246</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3702</v>
+        <v>-0.0625</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0314</v>
+        <v>0.3403</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0376</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.1142</v>
-      </c>
+        <v>0.0699</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1220,26 +1140,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.0283</v>
+        <v>0.064</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0929</v>
+        <v>-0.0595</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.162</v>
+        <v>0.2236</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1604</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-0.1661</v>
-      </c>
+        <v>0.041</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1247,26 +1164,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0665</v>
+        <v>0.0299</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2309</v>
+        <v>0.0225</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-0.0419</v>
-      </c>
+        <v>-0.1813</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1274,26 +1188,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.026</v>
+        <v>-0.0457</v>
       </c>
       <c r="D29" t="n">
-        <v>0.047</v>
+        <v>0.1551</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1025</v>
+        <v>-0.0143</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1049</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-0.2263</v>
-      </c>
+        <v>-0.09379999999999999</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1301,26 +1212,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.0878</v>
+        <v>-0.0121</v>
       </c>
       <c r="D30" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0467</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1649</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-0.1398</v>
-      </c>
+        <v>-0.0775</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1328,26 +1236,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0125</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0924</v>
+        <v>0.0392</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0684</v>
+        <v>0.0017</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0459</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.0121</v>
-      </c>
+        <v>-0.0751</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1355,26 +1260,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.124</v>
+        <v>-0.0144</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0738</v>
+        <v>0.0481</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0844</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.01</v>
-      </c>
+        <v>-0.0211</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1382,26 +1284,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0076</v>
+        <v>-0.0282</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0452</v>
+        <v>0.0457</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0143</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0214</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-0.0505</v>
-      </c>
+        <v>0.0005</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
